--- a/25_Архив/Архив_версий.xlsx
+++ b/25_Архив/Архив_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Архив версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Архив версий'!$A$1:$F$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Архив версий'!$A$1:$F$12</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
   <si>
     <t xml:space="preserve">Документ</t>
   </si>
@@ -128,6 +128,21 @@
   </si>
   <si>
     <t xml:space="preserve">25_Архив/2026-07-11_ИНС-001_drafts/ИНС-001_Запуск_циркуляционного_насоса_v0.91.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заменена v1.3 (добавлена ссылка на новый РГЛ-002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25_Архив/2026-07-11_v1.2_to_v1.3/СТД-002_Диагностика_водогрейных_котлов_v1.2.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заменена v1.3 (добавлены ссылки на новый РГЛ-003 и ИНС-001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25_Архив/2026-07-11_v1.2_to_v1.3/СТД-003_Диагностика_циркуляционных_насосов_v1.2.docx</t>
   </si>
 </sst>
 </file>
@@ -238,8 +253,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -532,218 +551,258 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>34</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F12"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/25_Архив/Архив_версий.xlsx
+++ b/25_Архив/Архив_версий.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Архив версий" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Архив версий'!$A$1:$F$12</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Архив версий'!$A$1:$F$13</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
   <si>
     <t xml:space="preserve">Документ</t>
   </si>
@@ -143,6 +143,18 @@
   </si>
   <si>
     <t xml:space="preserve">25_Архив/2026-07-11_v1.2_to_v1.3/СТД-003_Диагностика_циркуляционных_насосов_v1.2.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заменена v1.4 (добавлена ссылка на новые СТД-004/005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25_Архив/2026-07-12_v1.3_to_v1.4/СТД-002_Диагностика_водогрейных_котлов_v1.3.docx</t>
   </si>
 </sst>
 </file>
@@ -258,15 +270,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -551,7 +563,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="14"/>
@@ -761,7 +773,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
@@ -781,7 +793,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -801,8 +813,28 @@
         <v>39</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F13"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
